--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEBF107-78F3-4CB5-B512-F4A7C4CBA9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A6AB40-A0FB-43C1-BDA8-25CC7CFA4385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="2220" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="4" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
     <sheet name="Administrador" sheetId="12" r:id="rId2"/>
-    <sheet name="ConjuntoResidencial" sheetId="2" r:id="rId3"/>
-    <sheet name="Zonainmueble" sheetId="15" r:id="rId4"/>
-    <sheet name="Inmueble" sheetId="16" r:id="rId5"/>
-    <sheet name="ZonaComun" sheetId="4" r:id="rId6"/>
+    <sheet name="Inmueble(entidad importante)" sheetId="20" r:id="rId3"/>
+    <sheet name="ConjuntoResidencial" sheetId="2" r:id="rId4"/>
+    <sheet name="Zonainmueble" sheetId="15" r:id="rId5"/>
+    <sheet name="TipoZonaInmueble" sheetId="19" r:id="rId6"/>
+    <sheet name="Inmueble" sheetId="16" r:id="rId7"/>
+    <sheet name="TipoInmueble" sheetId="18" r:id="rId8"/>
+    <sheet name="ZonaComun" sheetId="4" r:id="rId9"/>
+    <sheet name="UnidadTiempoUso" sheetId="17" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="194">
   <si>
     <t>Nombre</t>
   </si>
@@ -532,9 +536,6 @@
     <t>imagen</t>
   </si>
   <si>
-    <t>Este es le dato que representa el tiempo de uso por numero entero de un residente</t>
-  </si>
-  <si>
     <t>Es un dato que representa el numero de contacto de la recepción del conjunto residencial.</t>
   </si>
   <si>
@@ -551,13 +552,88 @@
   </si>
   <si>
     <t>Objeto de dominio que representa un imnueble dentro de una zona de inmuebles en un conjunto residencial describe las caracteristicas especificasde una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona inmueble.</t>
+  </si>
+  <si>
+    <t>nombre ConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>Nombre Admin</t>
+  </si>
+  <si>
+    <t>vivienda</t>
+  </si>
+  <si>
+    <t>pardffdndddfdfdi</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>Objeto de dominio que representa un tipo de zona inmueble encargado de hacer la creación de nuevas zonas inmuebles para el conjunto residencial como torres, bloques , manzanas etc .</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada tipo zona imueble sea única.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa al nombre de un tipo de zona inmueble.</t>
+  </si>
+  <si>
+    <t>No es posible tener más de un tipo zona inmueble con el mismo nombre del tipo zona inmueble  para un mismo conjunto residencial.</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada tipo inmueble sea único.</t>
+  </si>
+  <si>
+    <t>TipoInmueble</t>
+  </si>
+  <si>
+    <t>Objeto de dominio que representa un tipo de inmueble encargado de hacer la creación de nuevos tipos inmuebles para el conjunto residencial como casas, apartamentos, glamplins  etc .</t>
+  </si>
+  <si>
+    <t>Es un dato que representa al nombre de un tipo inmueble como Casa, apartamento ETC.</t>
+  </si>
+  <si>
+    <t>No es posible tener mas de un tipo inmueble que tenga el mismo nombre.</t>
+  </si>
+  <si>
+    <t>Este es le dato que representa el tiempo de uso por numero entero positivo de un residente</t>
+  </si>
+  <si>
+    <t>UnidadTiempoUso</t>
+  </si>
+  <si>
+    <t>Objeto de dominio que representa una unidad de tiempo encargado de asignar la manera en como se va a medir el tiempo de unos de una persona según las necesidades o claridad de uso para un residente en una zona común .</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada unidad de tiempo de uso sea unica.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el formato de texto de una descripción para una unidad de tiempo de uso para un residente.</t>
+  </si>
+  <si>
+    <t>No es posible tener más de un tiempo de uso con el mismo nombre.</t>
+  </si>
+  <si>
+    <t>Unidad que representa 60 segundos.</t>
+  </si>
+  <si>
+    <t>Unidad de tiempo que representa un seguno</t>
+  </si>
+  <si>
+    <t>Segundo</t>
+  </si>
+  <si>
+    <t>Minuto</t>
+  </si>
+  <si>
+    <t>Unidad que representa 60 minutos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,6 +697,14 @@
     <font>
       <b/>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -700,7 +784,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -772,6 +856,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1107,14 +1195,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3601F120-B689-4608-A7AB-FD2F4140FEAD}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="58.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1122,44 +1210,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1167,8 +1279,164 @@
     <hyperlink ref="A2" location="ConjuntoResidencial!A1" display="ConjuntoResidencial" xr:uid="{D0048307-89EE-4AA5-9AB4-3B1D102BE25E}"/>
     <hyperlink ref="A3" location="ZonaComun!A1" display="ZonaComun" xr:uid="{FC7C1AA5-A8DF-4420-A7B0-922F74CE2B62}"/>
     <hyperlink ref="A4" location="Administrador!A1" display="Administrador" xr:uid="{B710B2E9-3802-4D37-8286-1D82A855E5A3}"/>
-    <hyperlink ref="A5" location="Zonainmueble!A1" display="ZonaInmueble" xr:uid="{A38EA035-AAF7-4A33-B542-4B528AF3BBC4}"/>
-    <hyperlink ref="A6" location="Inmueble!A1" display="Inmueble" xr:uid="{9B95D934-BD10-4DA6-9270-D48A389ACDE8}"/>
+    <hyperlink ref="A7" location="Zonainmueble!A1" display="ZonaInmueble" xr:uid="{A38EA035-AAF7-4A33-B542-4B528AF3BBC4}"/>
+    <hyperlink ref="A9" location="Inmueble!A1" display="Inmueble" xr:uid="{9B95D934-BD10-4DA6-9270-D48A389ACDE8}"/>
+    <hyperlink ref="A5" location="TipoZonaInmueble!A1" display="TipoZonaInmueble" xr:uid="{24258088-E516-451E-80FB-AE29EDA30CE5}"/>
+    <hyperlink ref="A6" location="TipoInmueble!A1" display="TipoInmueble" xr:uid="{D4BC0F34-341A-436B-8F9C-EA762CAD70FA}"/>
+    <hyperlink ref="A8" location="UnidadTiempoUso!A1" display="UnidadTiempoUso" xr:uid="{98F29D1F-9618-4F37-AE3F-1EE341BE19B3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2269DB9A-BACD-464C-9543-8BA126B4A282}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:8" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="20" t="str">
+        <f>B4</f>
+        <v>Segundo</v>
+      </c>
+      <c r="H4" s="36"/>
+    </row>
+    <row r="5" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="20" t="str">
+        <f>B5</f>
+        <v>Minuto</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f>B6</f>
+        <v>Hora</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="35"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="15"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Objetos de dominio'!A3" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{62CE3F1E-7A75-4D0D-A89D-14D91B8A6712}"/>
+    <hyperlink ref="D1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{14E022A0-311E-46EE-A8A9-16F85686ED20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1177,22 +1445,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3124B0-BF43-4D8E-8B80-2D2432DEB873}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="34.28515625" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" customWidth="1"/>
-    <col min="11" max="11" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="25.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="34.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.33203125" customWidth="1"/>
+    <col min="11" max="11" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>5</v>
       </c>
@@ -1204,7 +1472,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:11" s="29" customFormat="1" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="29" customFormat="1" ht="73.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1239,7 +1507,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1274,7 +1542,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -1312,7 +1580,7 @@
         <v>carlos@example.com</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>2</v>
       </c>
@@ -1350,7 +1618,7 @@
         <v>sara@gmail.com</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>3</v>
       </c>
@@ -1388,7 +1656,7 @@
         <v>maria.gonzalez@example.com</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
@@ -1426,7 +1694,7 @@
         <v>laura.martinez@example.com</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>5</v>
       </c>
@@ -1464,7 +1732,7 @@
         <v>andres.lopez@example.com</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
@@ -1518,18 +1786,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2670FA8A-36A3-4225-9DD4-768C3015DA5E}">
+  <dimension ref="A2:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCBB1F3-C6CB-4282-9EE1-3BEE3EA280EE}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="6" width="21.7109375" customWidth="1"/>
+    <col min="2" max="6" width="21.6640625" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="43.85546875" customWidth="1"/>
-    <col min="9" max="9" width="34.28515625" customWidth="1"/>
-    <col min="10" max="10" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.88671875" customWidth="1"/>
+    <col min="9" max="9" width="34.33203125" customWidth="1"/>
+    <col min="10" max="10" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>5</v>
       </c>
@@ -1543,7 +1841,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>12</v>
       </c>
@@ -1560,7 +1858,7 @@
         <v>53</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>137</v>
@@ -1575,7 +1873,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>6</v>
       </c>
@@ -1607,7 +1905,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -1642,7 +1940,7 @@
         <v>3053451564</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>2</v>
       </c>
@@ -1677,7 +1975,7 @@
         <v>3057477789</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1712,7 +2010,7 @@
         <v>3001234567</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1747,7 +2045,7 @@
         <v>3207654321</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1801,18 +2099,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615584B6-BB9C-4024-AABA-069882FFA83A}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="37.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>5</v>
       </c>
@@ -1821,7 +2119,7 @@
       <c r="D1" s="34"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" s="30" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>117</v>
       </c>
@@ -1838,11 +2136,11 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1855,11 +2153,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="31">
@@ -1874,11 +2172,11 @@
         <v>Torre1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="31">
@@ -1893,11 +2191,11 @@
         <v>Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="31">
@@ -1912,11 +2210,11 @@
         <v>Torre2 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="31">
@@ -1931,11 +2229,11 @@
         <v>Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="31">
@@ -1950,11 +2248,11 @@
         <v>Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="31">
@@ -1969,11 +2267,11 @@
         <v>Bloque1 - Riogrande</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="31">
@@ -1988,11 +2286,11 @@
         <v>Bloque1 - Ventus</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31">
@@ -2007,11 +2305,11 @@
         <v>Torre1 - Bolivar</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="31">
@@ -2048,24 +2346,138 @@
     <hyperlink ref="D11" location="ConjuntoResidencial!A7" display="ConjuntoResidencial!A7" xr:uid="{466D4C91-E5E2-4912-BD49-0C66AEDD1636}"/>
     <hyperlink ref="D12" location="ConjuntoResidencial!A6" display="ConjuntoResidencial!A6" xr:uid="{BB64C223-5AFB-4870-A3BB-24CF127D7640}"/>
     <hyperlink ref="D5:D6" location="ConjuntoResidencial!A4" display="1-Forest apartamentos" xr:uid="{5CC81003-F511-4F2E-A2EA-670B8730565A}"/>
+    <hyperlink ref="B3" location="TipoZonaInmueble!A1" display="tipoZonaInmueble" xr:uid="{A8CF1389-F6A1-4D96-8017-6FCE3D7C3EF0}"/>
+    <hyperlink ref="B4" location="TipoZonaInmueble!A4" display="Torre" xr:uid="{C1B80E09-0FAC-4134-B6EB-7E254D267951}"/>
+    <hyperlink ref="B5" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{CDD47B75-A09F-4637-AFD9-A7D8A66A0762}"/>
+    <hyperlink ref="B6" location="TipoZonaInmueble!A4" display="Torre" xr:uid="{1EFB8E94-E0D3-43DF-B045-806C42EF289D}"/>
+    <hyperlink ref="B7" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{1A44D43B-5D27-4D22-97D9-E14468D20271}"/>
+    <hyperlink ref="B8" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{63F41A7F-E41A-428F-B2BC-EE42338A6F8B}"/>
+    <hyperlink ref="B9" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{CB23F696-1084-494D-9224-B32B9EF1AFA0}"/>
+    <hyperlink ref="B10" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{91AB2238-B4AA-42A2-8CDA-ABF004AC2B8E}"/>
+    <hyperlink ref="B11" location="TipoZonaInmueble!A4" display="Torre" xr:uid="{8E811391-7941-4E4B-9C03-21461911A8C8}"/>
+    <hyperlink ref="B12" location="TipoZonaInmueble!A5" display="Bloque" xr:uid="{A4C1CC28-D434-468B-9C97-798C1861F4C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D27BCFB-C89E-4FFE-90C7-7E51A167EBA9}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <f>_xlfn.CONCAT(B4)</f>
+        <v>Torre</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <f t="shared" ref="C5:C8" si="0">_xlfn.CONCAT(B5)</f>
+        <v>Bloque</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B8" xr:uid="{81FA230B-6ECE-47C6-987E-253874E07B29}">
+      <formula1>$A$8:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{FF3E7648-688E-4978-AA7C-614DD208D7B7}"/>
+    <hyperlink ref="A1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{78B80C38-CE1E-43E7-98A2-4FE9A8FA95D2}"/>
+    <hyperlink ref="A1:B1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{7411190A-1C39-46CB-81A1-F1A0D3F39203}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488BF9E0-DC4F-43E4-93DE-0EE5B6337FDE}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
-    <col min="5" max="5" width="49.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="5" max="5" width="49.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>5</v>
       </c>
@@ -2074,7 +2486,7 @@
       <c r="D1" s="34"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>114</v>
       </c>
@@ -2091,11 +2503,11 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2108,11 +2520,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="1">
@@ -2127,11 +2539,11 @@
         <v>Apartamento102 - Torre1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="1">
@@ -2146,11 +2558,11 @@
         <v>Casa10 - Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="1">
@@ -2165,11 +2577,11 @@
         <v>Apartamento304 - Torre2 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="31">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C7" s="1">
@@ -2184,11 +2596,11 @@
         <v>Casa11 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="31">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="1">
@@ -2203,11 +2615,11 @@
         <v>Apartamento423 - Bloque1 - Ventus</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="1">
@@ -2222,11 +2634,11 @@
         <v>Apartamento1204 - Torre1 - Bolivar</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="1">
@@ -2241,11 +2653,11 @@
         <v>Casa5 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="32">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="1">
@@ -2260,11 +2672,11 @@
         <v>Casa17 - Bloque2 - Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="31">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="1">
@@ -2279,11 +2691,11 @@
         <v>Apartamento514 - Bloque1 - Riogrande</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="31">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="1">
@@ -2303,7 +2715,7 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B10" xr:uid="{BFBC3516-F07A-4FAF-AC89-9487897222A7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B13" xr:uid="{BFBC3516-F07A-4FAF-AC89-9487897222A7}">
       <formula1>$A$14:$A$15</formula1>
     </dataValidation>
   </dataValidations>
@@ -2321,27 +2733,158 @@
     <hyperlink ref="D11" location="Zonainmueble!A12" display="Zonainmueble!A12" xr:uid="{62275898-A78C-4C3F-8869-87870883AC94}"/>
     <hyperlink ref="D12" location="Zonainmueble!A9" display="Zonainmueble!A9" xr:uid="{47174CD0-D9E4-405D-BC4F-18241A565D3A}"/>
     <hyperlink ref="D13" location="Zonainmueble!A7" display="Zonainmueble!A7" xr:uid="{188EBF7F-FB28-40C9-B97F-611DB833F18F}"/>
+    <hyperlink ref="B3" location="TipoInmueble!A1" display="tipoInmueble" xr:uid="{5500C4CE-8763-44B3-BC3B-C4254F3515D2}"/>
+    <hyperlink ref="B4" location="TipoInmueble!A4" display="Apartamento" xr:uid="{C09ED20A-DC76-4EEA-8CB5-F1D3D3FB0493}"/>
+    <hyperlink ref="B5" location="TipoInmueble!A5" display="Casa" xr:uid="{432960CB-0403-48D8-8AE2-3EB129D2C3B6}"/>
+    <hyperlink ref="B6" location="TipoInmueble!A4" display="Apartamento" xr:uid="{90B32AAC-ED4F-4F86-A5B1-A6EEA507E098}"/>
+    <hyperlink ref="B8" location="TipoInmueble!A4" display="Apartamento" xr:uid="{0515E277-45E7-458B-88FD-2E7E627EAC20}"/>
+    <hyperlink ref="B9" location="TipoInmueble!A4" display="Apartamento" xr:uid="{FF142DB0-5150-4494-9F9F-D0A302F5C7FB}"/>
+    <hyperlink ref="B12" location="TipoInmueble!A4" display="Apartamento" xr:uid="{2FFA6466-1D9E-4BCA-9275-E829EC352A64}"/>
+    <hyperlink ref="B7" location="TipoInmueble!A5" display="Casa" xr:uid="{05220399-2FDE-4059-94E1-CBD893074E94}"/>
+    <hyperlink ref="B10" location="TipoInmueble!A5" display="Casa" xr:uid="{0A15F3C0-AB6E-457E-A80F-3CDDC90956FE}"/>
+    <hyperlink ref="B11" location="TipoInmueble!A5" display="Casa" xr:uid="{E80BBABF-AA63-4FD6-8423-0EB9A1F7C2D6}"/>
+    <hyperlink ref="B13" location="TipoInmueble!A5" display="Casa" xr:uid="{95493657-D854-4D1D-9477-7FD0BA01477A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAC0C45-73E0-49A7-B0D2-05CBF4DE566D}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="32">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <f>B4</f>
+        <v>Apartamento</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="31">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="9" t="str">
+        <f t="shared" ref="C5:C13" si="0">B5</f>
+        <v>Casa</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="31"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="32"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="31"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B10" xr:uid="{830C9500-F2E0-4145-8C00-79EC90581CBC}">
+      <formula1>$A$14:$A$15</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{9931E72A-F31F-4793-8C6E-58A87F58C2F6}"/>
+    <hyperlink ref="A1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{753F073C-ECD6-440C-8F79-90386215C748}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3E3BD9-49ED-471B-BA3A-A84E923CE558}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="7" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
-    <col min="10" max="10" width="33.140625" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" customWidth="1"/>
+    <col min="5" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="11" max="11" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -2355,7 +2898,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>26</v>
       </c>
@@ -2372,7 +2915,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="G2" s="23" t="s">
         <v>161</v>
@@ -2387,7 +2930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2406,7 +2949,7 @@
       <c r="F3" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>160</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -2419,7 +2962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -2436,9 +2979,9 @@
         <v>50</v>
       </c>
       <c r="F4" s="18">
-        <v>60</v>
-      </c>
-      <c r="G4" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -2453,7 +2996,7 @@
         <v>Piscina-Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -2472,7 +3015,7 @@
       <c r="F5" s="21">
         <v>120</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H5" s="22" t="s">
@@ -2487,7 +3030,7 @@
         <v>Gimnasio-Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -2506,7 +3049,7 @@
       <c r="F6" s="21">
         <v>1</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2521,7 +3064,7 @@
         <v>piscinaAdultos-Natural</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -2540,7 +3083,7 @@
       <c r="F7" s="21">
         <v>4</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="19" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="22" t="s">
@@ -2555,7 +3098,7 @@
         <v>Salón de Eventos-Riogrande</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -2574,7 +3117,7 @@
       <c r="F8" s="21">
         <v>90</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H8" s="22" t="s">
@@ -2589,7 +3132,7 @@
         <v>Cancha de Fútbol-Bolivar</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -2608,7 +3151,7 @@
       <c r="F9" s="21">
         <v>45</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H9" s="22" t="s">
@@ -2623,7 +3166,7 @@
         <v>Piscina Pequeña-Natural</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -2642,7 +3185,7 @@
       <c r="F10" s="21">
         <v>2</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="19" t="s">
         <v>49</v>
       </c>
       <c r="H10" s="22" t="s">
@@ -2657,7 +3200,7 @@
         <v>Zona BBQ-Ventus</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -2676,7 +3219,7 @@
       <c r="F11" s="21">
         <v>60</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H11" s="22" t="s">
@@ -2691,7 +3234,7 @@
         <v>Cancha de Tenis-Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -2710,7 +3253,7 @@
       <c r="F12" s="21">
         <v>90</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="19" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="22" t="s">
@@ -2725,18 +3268,18 @@
         <v>Sala de Juegos-Forest apartamentos</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="17"/>
       <c r="C13" s="16"/>
       <c r="D13" s="15"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="16"/>
       <c r="D14" s="15"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" s="16"/>
       <c r="D15" s="15"/>
       <c r="H15" s="15"/>
@@ -2750,6 +3293,16 @@
     <hyperlink ref="I4" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{B8DE4DDD-37E7-4134-B07B-380ED9355EAE}"/>
     <hyperlink ref="I5" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{9C185349-1620-4637-ACB0-760A61F04D2F}"/>
     <hyperlink ref="I6" location="ConjuntoResidencial!A5" display="ConjuntoResidencial!A5" xr:uid="{7582E04B-7A1B-430D-B8C9-B08941E36695}"/>
+    <hyperlink ref="G3" location="UnidadTiempoUso!A1" display="unidadTiempoUso" xr:uid="{4471858B-F7DA-4618-B7D5-DE41707CC801}"/>
+    <hyperlink ref="G4" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{9F89C364-56C3-412D-937D-C309AFC5905B}"/>
+    <hyperlink ref="G6" location="UnidadTiempoUso!A6" display="Hora" xr:uid="{757F0AB7-9A4E-42E3-8A14-1A712F179345}"/>
+    <hyperlink ref="G5" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{DDF89C72-9F73-4B15-BD02-06DFFEDCCFC9}"/>
+    <hyperlink ref="G8" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{96008917-17CA-458D-BACF-708872C32EC9}"/>
+    <hyperlink ref="G9" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{CC092EBD-AA23-406B-87C0-2199DA39AA12}"/>
+    <hyperlink ref="G11" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{82BE2B96-F770-4C24-B067-E6E66CD715C5}"/>
+    <hyperlink ref="G12" location="UnidadTiempoUso!A5" display="Minutos" xr:uid="{82ED7FAE-1D5A-48C0-996D-532A66DD3EAE}"/>
+    <hyperlink ref="G7" location="UnidadTiempoUso!A6" display="Hora" xr:uid="{0817EE55-65FB-4BA1-9630-3B5B60F2D1AE}"/>
+    <hyperlink ref="G10" location="UnidadTiempoUso!A6" display="Hora" xr:uid="{FE62DCC6-FEB0-4EB7-BDB1-215A06600501}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A6AB40-A0FB-43C1-BDA8-25CC7CFA4385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBD79EC-C9FC-4E8B-B0DA-D5099AB3220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="205">
   <si>
     <t>Nombre</t>
   </si>
@@ -554,18 +554,6 @@
     <t>Objeto de dominio que representa un imnueble dentro de una zona de inmuebles en un conjunto residencial describe las caracteristicas especificasde una unidad habitacional en el contexto de una agrupación más amplia, como una torre, bloque o área específica, que es representada por su zona inmueble.</t>
   </si>
   <si>
-    <t>nombre ConjuntoResidencial</t>
-  </si>
-  <si>
-    <t>Nombre Admin</t>
-  </si>
-  <si>
-    <t>vivienda</t>
-  </si>
-  <si>
-    <t>pardffdndddfdfdi</t>
-  </si>
-  <si>
     <t>TipoZonaInmueble</t>
   </si>
   <si>
@@ -627,6 +615,51 @@
   </si>
   <si>
     <t>Unidad que representa 60 minutos.</t>
+  </si>
+  <si>
+    <t>ConjuntoResidencial(Identificador)</t>
+  </si>
+  <si>
+    <t>ConjuntoResidencial(Nombre)</t>
+  </si>
+  <si>
+    <t>Inmueble(NumeroVivienda)</t>
+  </si>
+  <si>
+    <t>TipoInmueble(Identificador)</t>
+  </si>
+  <si>
+    <t>TipoInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Identificador)</t>
+  </si>
+  <si>
+    <t>TipoZonaInmueble(Nombre)</t>
+  </si>
+  <si>
+    <t>ZonaInmueble(NumeroZonaInmueble)</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el formato numero entero del numero de la vivienda donde esta hospedado el residente.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el identificador de un tipo de zona inmueble.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el nombre de un tipo de inmueble donde hospeda el residente.</t>
+  </si>
+  <si>
+    <t>es un dato que representa el indetificador de un tipo de zona inmuelble.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa el nombre de un tipo de zoba  inmueble donde hospeda el residente.</t>
+  </si>
+  <si>
+    <t>Este dato representa el numero asignado para una zona inmueble de un conjunto residencial</t>
+  </si>
+  <si>
+    <t>No es posiible tener una informacion repetida para la consulta de otro residente.</t>
   </si>
 </sst>
 </file>
@@ -784,7 +817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -853,13 +886,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1236,18 +1275,18 @@
     </row>
     <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -1260,10 +1299,10 @@
     </row>
     <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72" x14ac:dyDescent="0.3">
@@ -1310,16 +1349,16 @@
     </row>
     <row r="2" spans="1:8" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>161</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1341,26 +1380,26 @@
         <v>1</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D4" s="20" t="str">
         <f>B4</f>
         <v>Segundo</v>
       </c>
-      <c r="H4" s="36"/>
+      <c r="H4" s="35"/>
     </row>
     <row r="5" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D5" s="20" t="str">
         <f>B5</f>
@@ -1375,7 +1414,7 @@
         <v>49</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D6" s="20" t="str">
         <f>B6</f>
@@ -1422,7 +1461,7 @@
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="35"/>
+      <c r="D13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C14" s="15"/>
@@ -1461,14 +1500,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
@@ -1787,30 +1826,407 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2670FA8A-36A3-4225-9DD4-768C3015DA5E}">
-  <dimension ref="A2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="43.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>172</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D4" s="32">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="32">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="37">
+        <v>5</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f>_xlfn.CONCAT(A4,B4,"-",F4,G4,"-",H4,"-",D4,E4,"-",C4)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-1204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>205</v>
+      </c>
+      <c r="D5" s="32">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="37">
+        <v>5</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f>_xlfn.CONCAT(A5,B5,"-",F5,G5,"-",H5,"-",D5,E5,"-",C5)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1">
+        <v>514</v>
+      </c>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="31">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="38">
+        <v>3</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f t="shared" ref="I6:I13" si="0">_xlfn.CONCAT(A6,B6,"-",F6,G6,"-",H6,"-",D6,E6,"-",C6)</f>
+        <v>2Natural-2Bloque-3-2Casa-514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="31">
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="31">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="38">
+        <v>3</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>2Natural-2Bloque-3-2Casa-23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1">
+        <v>204</v>
+      </c>
+      <c r="D8" s="32">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="38">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-2-1Apartamento-204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="31">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="31">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="38">
+        <v>8</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2Bloque-8-2Casa-8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1">
+        <v>306</v>
+      </c>
+      <c r="D10" s="32">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="38">
+        <v>7</v>
+      </c>
+      <c r="I10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-7-1Apartamento-306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="31">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="31">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="38">
+        <v>7</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2Bloque-7-2Casa-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1">
+        <v>501</v>
+      </c>
+      <c r="D12" s="32">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="32">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="38">
+        <v>7</v>
+      </c>
+      <c r="I12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>5Ventus-1Torre-7-1Apartamento-501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="31">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="31">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="38">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>5Ventus-2Bloque-1-2Casa-9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E13" xr:uid="{97573631-C058-4501-BD54-1454199800AE}">
+      <formula1>$A$14:$A$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{F7F7B960-87B4-463F-A9AB-BCF5AFE358F1}">
+      <formula1>$A$8:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{0B6C98B6-F660-457D-BFAF-FAFEA3C022A9}"/>
+    <hyperlink ref="A1:F1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{8ABC13BC-C829-404A-8904-ECAF31EF7A31}"/>
+    <hyperlink ref="I1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{6BEE998A-D5A7-4B16-BE98-5FFC09DB1C95}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1828,14 +2244,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2111,12 +2527,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2371,21 +2787,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="36"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2478,12 +2894,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2760,21 +3176,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
+      <c r="B1" s="36"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>178</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2808,7 +3224,7 @@
         <v>47</v>
       </c>
       <c r="C5" s="9" t="str">
-        <f t="shared" ref="C5:C13" si="0">B5</f>
+        <f t="shared" ref="C5" si="0">B5</f>
         <v>Casa</v>
       </c>
     </row>
@@ -2915,7 +3331,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G2" s="23" t="s">
         <v>161</v>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBD79EC-C9FC-4E8B-B0DA-D5099AB3220C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909C222-3D6B-42B0-A0AD-09EFA508FC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
+    <workbookView xWindow="19680" yWindow="2565" windowWidth="23625" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="214">
   <si>
     <t>Nombre</t>
   </si>
@@ -660,6 +660,33 @@
   </si>
   <si>
     <t>No es posiible tener una informacion repetida para la consulta de otro residente.</t>
+  </si>
+  <si>
+    <t>abreviatura</t>
+  </si>
+  <si>
+    <t>enBase</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Es un dato que respresenta en texto como queda abreviada la unidad especifica.</t>
+  </si>
+  <si>
+    <t>Es un dato logico que reprenta que unidad esta activa para medir el tiempo de uso permitido para que un residente use una zona común.</t>
   </si>
 </sst>
 </file>
@@ -890,14 +917,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1235,13 +1262,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3601F120-B689-4608-A7AB-FD2F4140FEAD}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1257,7 +1284,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -1265,7 +1292,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1273,7 +1300,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>169</v>
       </c>
@@ -1281,7 +1308,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>175</v>
       </c>
@@ -1289,7 +1316,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -1297,7 +1324,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>180</v>
       </c>
@@ -1305,7 +1332,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
@@ -1330,24 +1357,26 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2269DB9A-BACD-464C-9543-8BA126B4A282}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
+    <col min="2" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>182</v>
       </c>
@@ -1355,13 +1384,19 @@
         <v>161</v>
       </c>
       <c r="C2" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="F2" s="23" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1369,113 +1404,151 @@
         <v>160</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>1</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="20" t="str">
+      <c r="F4" s="20" t="str">
         <f>B4</f>
         <v>Segundo</v>
       </c>
-      <c r="H4" s="35"/>
-    </row>
-    <row r="5" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="35"/>
+    </row>
+    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="F5" s="20" t="str">
         <f>B5</f>
         <v>Minuto</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="F6" s="20" t="str">
         <f>B6</f>
         <v>Hora</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="20"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="21"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="20"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="20"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="15"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C15" s="15"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="15"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="15"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E16" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de dominio'!A3" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{62CE3F1E-7A75-4D0D-A89D-14D91B8A6712}"/>
-    <hyperlink ref="D1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{14E022A0-311E-46EE-A8A9-16F85686ED20}"/>
+    <hyperlink ref="F1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{14E022A0-311E-46EE-A8A9-16F85686ED20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1484,34 +1557,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3124B0-BF43-4D8E-8B80-2D2432DEB873}">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="25.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="34.33203125" customWidth="1"/>
-    <col min="10" max="10" width="21.33203125" customWidth="1"/>
-    <col min="11" max="11" width="27.109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="34.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" customWidth="1"/>
+    <col min="11" max="11" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:11" s="29" customFormat="1" ht="73.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="29" customFormat="1" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1546,7 +1619,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1581,7 +1654,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -1619,7 +1692,7 @@
         <v>carlos@example.com</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>2</v>
       </c>
@@ -1657,7 +1730,7 @@
         <v>sara@gmail.com</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>3</v>
       </c>
@@ -1695,7 +1768,7 @@
         <v>maria.gonzalez@example.com</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>4</v>
       </c>
@@ -1733,7 +1806,7 @@
         <v>laura.martinez@example.com</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>5</v>
       </c>
@@ -1771,7 +1844,7 @@
         <v>andres.lopez@example.com</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>6</v>
       </c>
@@ -1827,32 +1900,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2670FA8A-36A3-4225-9DD4-768C3015DA5E}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>12</v>
       </c>
@@ -1881,7 +1954,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>190</v>
       </c>
@@ -1910,7 +1983,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -1932,7 +2005,7 @@
       <c r="G4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="36">
         <v>5</v>
       </c>
       <c r="I4" s="9" t="str">
@@ -1940,7 +2013,7 @@
         <v>1Forest apartamentos-1Torre-5-1Apartamento-1204</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -1962,7 +2035,7 @@
       <c r="G5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="36">
         <v>5</v>
       </c>
       <c r="I5" s="9" t="str">
@@ -1970,7 +2043,7 @@
         <v>1Forest apartamentos-1Torre-5-1Apartamento-205</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1992,7 +2065,7 @@
       <c r="G6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="37">
         <v>3</v>
       </c>
       <c r="I6" s="9" t="str">
@@ -2000,7 +2073,7 @@
         <v>2Natural-2Bloque-3-2Casa-514</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -2022,7 +2095,7 @@
       <c r="G7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="37">
         <v>3</v>
       </c>
       <c r="I7" s="9" t="str">
@@ -2030,7 +2103,7 @@
         <v>2Natural-2Bloque-3-2Casa-23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -2052,7 +2125,7 @@
       <c r="G8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="37">
         <v>2</v>
       </c>
       <c r="I8" s="9" t="str">
@@ -2060,7 +2133,7 @@
         <v>3Riogrande-1Torre-2-1Apartamento-204</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -2082,7 +2155,7 @@
       <c r="G9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="37">
         <v>8</v>
       </c>
       <c r="I9" s="9" t="str">
@@ -2090,7 +2163,7 @@
         <v>3Riogrande-2Bloque-8-2Casa-8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -2112,7 +2185,7 @@
       <c r="G10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="37">
         <v>7</v>
       </c>
       <c r="I10" s="9" t="str">
@@ -2120,7 +2193,7 @@
         <v>3Riogrande-1Torre-7-1Apartamento-306</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -2142,7 +2215,7 @@
       <c r="G11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="37">
         <v>7</v>
       </c>
       <c r="I11" s="9" t="str">
@@ -2150,7 +2223,7 @@
         <v>3Riogrande-2Bloque-7-2Casa-4</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -2172,7 +2245,7 @@
       <c r="G12" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="37">
         <v>7</v>
       </c>
       <c r="I12" s="9" t="str">
@@ -2180,7 +2253,7 @@
         <v>5Ventus-1Torre-7-1Apartamento-501</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>5</v>
       </c>
@@ -2202,7 +2275,7 @@
       <c r="G13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="37">
         <v>1</v>
       </c>
       <c r="I13" s="9" t="str">
@@ -2234,30 +2307,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCBB1F3-C6CB-4282-9EE1-3BEE3EA280EE}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="6" width="21.6640625" customWidth="1"/>
+    <col min="2" max="6" width="21.7109375" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="43.88671875" customWidth="1"/>
-    <col min="9" max="9" width="34.33203125" customWidth="1"/>
-    <col min="10" max="10" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.85546875" customWidth="1"/>
+    <col min="9" max="9" width="34.28515625" customWidth="1"/>
+    <col min="10" max="10" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>12</v>
       </c>
@@ -2289,7 +2362,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>6</v>
       </c>
@@ -2321,7 +2394,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -2356,7 +2429,7 @@
         <v>3053451564</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>2</v>
       </c>
@@ -2391,7 +2464,7 @@
         <v>3057477789</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2426,7 +2499,7 @@
         <v>3001234567</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2461,7 +2534,7 @@
         <v>3207654321</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2518,24 +2591,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615584B6-BB9C-4024-AABA-069882FFA83A}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="30" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>117</v>
       </c>
@@ -2552,7 +2625,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2569,7 +2642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -2588,7 +2661,7 @@
         <v>Torre1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2607,7 +2680,7 @@
         <v>Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -2626,7 +2699,7 @@
         <v>Torre2 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -2645,7 +2718,7 @@
         <v>Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -2664,7 +2737,7 @@
         <v>Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -2683,7 +2756,7 @@
         <v>Bloque1 - Riogrande</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2702,7 +2775,7 @@
         <v>Bloque1 - Ventus</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -2721,7 +2794,7 @@
         <v>Torre1 - Bolivar</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2780,20 +2853,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D27BCFB-C89E-4FFE-90C7-7E51A167EBA9}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="38"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" s="30" customFormat="1" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="30" customFormat="1" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>171</v>
       </c>
@@ -2804,7 +2877,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2815,7 +2888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -2827,7 +2900,7 @@
         <v>Torre</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2839,7 +2912,7 @@
         <v>Bloque</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="str">
@@ -2847,7 +2920,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="str">
@@ -2855,7 +2928,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="str">
@@ -2884,25 +2957,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488BF9E0-DC4F-43E4-93DE-0EE5B6337FDE}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
-    <col min="5" max="5" width="49.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="49.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>114</v>
       </c>
@@ -2919,7 +2992,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2936,7 +3009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
@@ -2955,7 +3028,7 @@
         <v>Apartamento102 - Torre1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -2974,7 +3047,7 @@
         <v>Casa10 - Bloque1 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>3</v>
       </c>
@@ -2993,7 +3066,7 @@
         <v>Apartamento304 - Torre2 - Forest apartamentos</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
         <v>4</v>
       </c>
@@ -3012,7 +3085,7 @@
         <v>Casa11 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="31">
         <v>5</v>
       </c>
@@ -3031,7 +3104,7 @@
         <v>Apartamento423 - Bloque1 - Ventus</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>6</v>
       </c>
@@ -3050,7 +3123,7 @@
         <v>Apartamento1204 - Torre1 - Bolivar</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>7</v>
       </c>
@@ -3069,7 +3142,7 @@
         <v>Casa5 - Bloque1 - Natural</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>8</v>
       </c>
@@ -3088,7 +3161,7 @@
         <v>Casa17 - Bloque2 - Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>9</v>
       </c>
@@ -3107,7 +3180,7 @@
         <v>Apartamento514 - Bloque1 - Riogrande</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>10</v>
       </c>
@@ -3168,21 +3241,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAC0C45-73E0-49A7-B0D2-05CBF4DE566D}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="38"/>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" spans="1:3" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="53.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>174</v>
       </c>
@@ -3193,18 +3266,18 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>1</v>
       </c>
@@ -3216,7 +3289,7 @@
         <v>Apartamento</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -3228,42 +3301,42 @@
         <v>Casa</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="31"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="31"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="31"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="31"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="31"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="32"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="31"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="31"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -3288,19 +3361,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3E3BD9-49ED-471B-BA3A-A84E923CE558}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
-    <col min="11" max="11" width="22.5546875" customWidth="1"/>
+    <col min="5" max="7" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="33.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -3314,7 +3387,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>26</v>
       </c>
@@ -3346,7 +3419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3378,7 +3451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -3412,7 +3485,7 @@
         <v>Piscina-Forest apartamentos</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -3446,7 +3519,7 @@
         <v>Gimnasio-Forest apartamentos</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -3480,7 +3553,7 @@
         <v>piscinaAdultos-Natural</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -3514,7 +3587,7 @@
         <v>Salón de Eventos-Riogrande</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -3548,7 +3621,7 @@
         <v>Cancha de Fútbol-Bolivar</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -3582,7 +3655,7 @@
         <v>Piscina Pequeña-Natural</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -3616,7 +3689,7 @@
         <v>Zona BBQ-Ventus</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -3650,7 +3723,7 @@
         <v>Cancha de Tenis-Riogrande</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -3684,18 +3757,18 @@
         <v>Sala de Juegos-Forest apartamentos</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="17"/>
       <c r="C13" s="16"/>
       <c r="D13" s="15"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C14" s="16"/>
       <c r="D14" s="15"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C15" s="16"/>
       <c r="D15" s="15"/>
       <c r="H15" s="15"/>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909C222-3D6B-42B0-A0AD-09EFA508FC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AF4AE6-CBF5-4A57-9F84-8E68F9993AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19680" yWindow="2565" windowWidth="23625" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
+    <workbookView xWindow="20070" yWindow="2400" windowWidth="18345" windowHeight="15345" firstSheet="7" activeTab="9" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
     <sheet name="Administrador" sheetId="12" r:id="rId2"/>
-    <sheet name="Inmueble(entidad importante)" sheetId="20" r:id="rId3"/>
-    <sheet name="ConjuntoResidencial" sheetId="2" r:id="rId4"/>
-    <sheet name="Zonainmueble" sheetId="15" r:id="rId5"/>
-    <sheet name="TipoZonaInmueble" sheetId="19" r:id="rId6"/>
-    <sheet name="Inmueble" sheetId="16" r:id="rId7"/>
-    <sheet name="TipoInmueble" sheetId="18" r:id="rId8"/>
-    <sheet name="ZonaComun" sheetId="4" r:id="rId9"/>
-    <sheet name="UnidadTiempoUso" sheetId="17" r:id="rId10"/>
+    <sheet name="ConjuntoResidencial" sheetId="2" r:id="rId3"/>
+    <sheet name="Zonainmueble" sheetId="15" r:id="rId4"/>
+    <sheet name="TipoZonaInmueble" sheetId="19" r:id="rId5"/>
+    <sheet name="Inmueble" sheetId="16" r:id="rId6"/>
+    <sheet name="TipoInmueble" sheetId="18" r:id="rId7"/>
+    <sheet name="ZonaComun" sheetId="4" r:id="rId8"/>
+    <sheet name="UnidadTiempoUso" sheetId="17" r:id="rId9"/>
+    <sheet name="Inmueble(entidad importante)" sheetId="20" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1356,199 +1356,407 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2269DB9A-BACD-464C-9543-8BA126B4A282}">
-  <dimension ref="A1:J16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2670FA8A-36A3-4225-9DD4-768C3015DA5E}">
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="33.140625" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1204</v>
+      </c>
+      <c r="D4" s="32">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="32">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="36">
+        <v>5</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f>_xlfn.CONCAT(A4,B4,"-",F4,G4,"-",H4,"-",D4,E4,"-",C4)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-1204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
         <v>205</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="D5" s="32">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="32">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="36">
+        <v>5</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f>_xlfn.CONCAT(A5,B5,"-",F5,G5,"-",H5,"-",D5,E5,"-",C5)</f>
+        <v>1Forest apartamentos-1Torre-5-1Apartamento-205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1">
+        <v>514</v>
+      </c>
+      <c r="D6" s="31">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="31">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="37">
+        <v>3</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f t="shared" ref="I6:I13" si="0">_xlfn.CONCAT(A6,B6,"-",F6,G6,"-",H6,"-",D6,E6,"-",C6)</f>
+        <v>2Natural-2Bloque-3-2Casa-514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="31">
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="31">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="37">
+        <v>3</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>2Natural-2Bloque-3-2Casa-23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1">
+        <v>204</v>
+      </c>
+      <c r="D8" s="32">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="32">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="37">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-2-1Apartamento-204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="31">
+        <v>2</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="31">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="37">
+        <v>8</v>
+      </c>
+      <c r="I9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2Bloque-8-2Casa-8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1">
+        <v>306</v>
+      </c>
+      <c r="D10" s="32">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="32">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="37">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+      <c r="I10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-1Torre-7-1Apartamento-306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="31">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="31">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="37">
+        <v>7</v>
+      </c>
+      <c r="I11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>3Riogrande-2Bloque-7-2Casa-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1">
+        <v>501</v>
+      </c>
+      <c r="D12" s="32">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F4" s="20" t="str">
-        <f>B4</f>
-        <v>Segundo</v>
-      </c>
-      <c r="J4" s="35"/>
-    </row>
-    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="E12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="32">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="37">
+        <v>7</v>
+      </c>
+      <c r="I12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>5Ventus-1Torre-7-1Apartamento-501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="31">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" s="20" t="str">
-        <f>B5</f>
-        <v>Minuto</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="20" t="str">
-        <f>B6</f>
-        <v>Hora</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="20"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="34"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E15" s="15"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E16" s="15"/>
+      <c r="E13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="31">
+        <v>2</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="37">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>5Ventus-2Bloque-1-2Casa-9</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E13" xr:uid="{97573631-C058-4501-BD54-1454199800AE}">
+      <formula1>$A$14:$A$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{F7F7B960-87B4-463F-A9AB-BCF5AFE358F1}">
+      <formula1>$A$8:$A$9</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="'Objetos de dominio'!A3" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{62CE3F1E-7A75-4D0D-A89D-14D91B8A6712}"/>
-    <hyperlink ref="F1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{14E022A0-311E-46EE-A8A9-16F85686ED20}"/>
+    <hyperlink ref="A1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{0B6C98B6-F660-457D-BFAF-FAFEA3C022A9}"/>
+    <hyperlink ref="A1:F1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{8ABC13BC-C829-404A-8904-ECAF31EF7A31}"/>
+    <hyperlink ref="I1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{6BEE998A-D5A7-4B16-BE98-5FFC09DB1C95}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1898,413 +2106,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2670FA8A-36A3-4225-9DD4-768C3015DA5E}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2" spans="1:9" s="28" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1204</v>
-      </c>
-      <c r="D4" s="32">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="32">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="36">
-        <v>5</v>
-      </c>
-      <c r="I4" s="9" t="str">
-        <f>_xlfn.CONCAT(A4,B4,"-",F4,G4,"-",H4,"-",D4,E4,"-",C4)</f>
-        <v>1Forest apartamentos-1Torre-5-1Apartamento-1204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1">
-        <v>205</v>
-      </c>
-      <c r="D5" s="32">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="32">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="36">
-        <v>5</v>
-      </c>
-      <c r="I5" s="9" t="str">
-        <f>_xlfn.CONCAT(A5,B5,"-",F5,G5,"-",H5,"-",D5,E5,"-",C5)</f>
-        <v>1Forest apartamentos-1Torre-5-1Apartamento-205</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="1">
-        <v>514</v>
-      </c>
-      <c r="D6" s="31">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="31">
-        <v>2</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="37">
-        <v>3</v>
-      </c>
-      <c r="I6" s="9" t="str">
-        <f t="shared" ref="I6:I13" si="0">_xlfn.CONCAT(A6,B6,"-",F6,G6,"-",H6,"-",D6,E6,"-",C6)</f>
-        <v>2Natural-2Bloque-3-2Casa-514</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>2</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1">
-        <v>23</v>
-      </c>
-      <c r="D7" s="31">
-        <v>2</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="31">
-        <v>2</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="37">
-        <v>3</v>
-      </c>
-      <c r="I7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>2Natural-2Bloque-3-2Casa-23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="1">
-        <v>204</v>
-      </c>
-      <c r="D8" s="32">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="32">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="37">
-        <v>2</v>
-      </c>
-      <c r="I8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>3Riogrande-1Torre-2-1Apartamento-204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="31">
-        <v>2</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="31">
-        <v>2</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="37">
-        <v>8</v>
-      </c>
-      <c r="I9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>3Riogrande-2Bloque-8-2Casa-8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="1">
-        <v>306</v>
-      </c>
-      <c r="D10" s="32">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="32">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="37">
-        <v>7</v>
-      </c>
-      <c r="I10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>3Riogrande-1Torre-7-1Apartamento-306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="1">
-        <v>4</v>
-      </c>
-      <c r="D11" s="31">
-        <v>2</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="31">
-        <v>2</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="37">
-        <v>7</v>
-      </c>
-      <c r="I11" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>3Riogrande-2Bloque-7-2Casa-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="1">
-        <v>501</v>
-      </c>
-      <c r="D12" s="32">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="32">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="37">
-        <v>7</v>
-      </c>
-      <c r="I12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>5Ventus-1Torre-7-1Apartamento-501</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="1">
-        <v>9</v>
-      </c>
-      <c r="D13" s="31">
-        <v>2</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="31">
-        <v>2</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="37">
-        <v>1</v>
-      </c>
-      <c r="I13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>5Ventus-2Bloque-1-2Casa-9</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E13" xr:uid="{97573631-C058-4501-BD54-1454199800AE}">
-      <formula1>$A$14:$A$15</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G13" xr:uid="{F7F7B960-87B4-463F-A9AB-BCF5AFE358F1}">
-      <formula1>$A$8:$A$9</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{0B6C98B6-F660-457D-BFAF-FAFEA3C022A9}"/>
-    <hyperlink ref="A1:F1" location="'Objetos de dominio'!A1" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{8ABC13BC-C829-404A-8904-ECAF31EF7A31}"/>
-    <hyperlink ref="I1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{6BEE998A-D5A7-4B16-BE98-5FFC09DB1C95}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CCBB1F3-C6CB-4282-9EE1-3BEE3EA280EE}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2588,7 +2389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{615584B6-BB9C-4024-AABA-069882FFA83A}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2850,7 +2651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D27BCFB-C89E-4FFE-90C7-7E51A167EBA9}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2954,7 +2755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488BF9E0-DC4F-43E4-93DE-0EE5B6337FDE}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3238,7 +3039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAC0C45-73E0-49A7-B0D2-05CBF4DE566D}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3358,7 +3159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3E3BD9-49ED-471B-BA3A-A84E923CE558}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3795,4 +3596,203 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2269DB9A-BACD-464C-9543-8BA126B4A282}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="33.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" s="33" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="20" t="str">
+        <f>B4</f>
+        <v>Segundo</v>
+      </c>
+      <c r="J4" s="35"/>
+    </row>
+    <row r="5" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="20" t="str">
+        <f>B5</f>
+        <v>Minuto</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" s="20" t="str">
+        <f>B6</f>
+        <v>Hora</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="15"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E16" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Objetos de dominio'!A3" display="&lt;&lt;&lt;&lt;&lt;&lt; Volver al inicio" xr:uid="{62CE3F1E-7A75-4D0D-A89D-14D91B8A6712}"/>
+    <hyperlink ref="F1" location="Objetos de dominio!A1" display="Objetos de dominio!A1" xr:uid="{14E022A0-311E-46EE-A8A9-16F85686ED20}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/ConjuntosResidenciales Muestro Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AF4AE6-CBF5-4A57-9F84-8E68F9993AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC27291-9693-4F5A-BF3E-8F4E1EC4969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20070" yWindow="2400" windowWidth="18345" windowHeight="15345" firstSheet="7" activeTab="9" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
+    <workbookView xWindow="1395" yWindow="3135" windowWidth="33960" windowHeight="15345" firstSheet="2" activeTab="7" xr2:uid="{46B52760-6E94-4759-BDEF-A2400BC5A0BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -1360,7 +1360,7 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
